--- a/data/trans_orig/P1416-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1416-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de alergias crónicas en 2007</t>
+          <t>Población con diagnóstico de alergias crónicas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26156</t>
+          <t>25670</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>48974</t>
+          <t>47287</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>45046</t>
+          <t>46352</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>73235</t>
+          <t>74495</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>77777</t>
+          <t>75677</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>113337</t>
+          <t>113411</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,7 +818,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>645038</t>
+          <t>646725</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>667856</t>
+          <t>668342</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>93,19%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,23%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>615116</t>
+          <t>613856</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>643305</t>
+          <t>641999</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1269026</t>
+          <t>1268952</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1304586</t>
+          <t>1306686</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -936,7 +936,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,37%</t>
+          <t>94,53%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>55620</t>
+          <t>56565</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>88558</t>
+          <t>89679</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>76176</t>
+          <t>75669</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>114032</t>
+          <t>114714</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,78%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>144391</t>
+          <t>142323</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>196033</t>
+          <t>191567</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>873242</t>
+          <t>872121</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>906180</t>
+          <t>905235</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,79%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>854361</t>
+          <t>853679</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>892217</t>
+          <t>892724</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,22%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1734160</t>
+          <t>1738626</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1785802</t>
+          <t>1787870</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,84%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,63%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29590</t>
+          <t>28483</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>54395</t>
+          <t>55151</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46854</t>
+          <t>46846</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>76061</t>
+          <t>74951</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>83517</t>
+          <t>82754</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>123255</t>
+          <t>120521</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,85%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>624114</t>
+          <t>623358</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>648919</t>
+          <t>650026</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,98%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>607780</t>
+          <t>608890</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>636987</t>
+          <t>636995</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1239095</t>
+          <t>1241829</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1278833</t>
+          <t>1279596</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,93%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>55091</t>
+          <t>57445</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>89130</t>
+          <t>88746</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,46%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>91860</t>
+          <t>91544</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>131945</t>
+          <t>131426</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,65%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>158533</t>
+          <t>157557</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>206445</t>
+          <t>208752</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>853092</t>
+          <t>853476</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>887131</t>
+          <t>884777</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,54%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>93,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>906667</t>
+          <t>907186</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>946752</t>
+          <t>947068</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,35%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1774389</t>
+          <t>1772082</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1822301</t>
+          <t>1823277</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,0%</t>
+          <t>92,05%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>194709</t>
+          <t>193186</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>253999</t>
+          <t>249909</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>289998</t>
+          <t>290318</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>360635</t>
+          <t>357888</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,59%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>498737</t>
+          <t>501629</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>587273</t>
+          <t>590728</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,88%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3022544</t>
+          <t>3026634</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3081834</t>
+          <t>3083357</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3018562</t>
+          <t>3021309</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3089199</t>
+          <t>3088879</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6068468</t>
+          <t>6065013</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6157004</t>
+          <t>6154112</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,46%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de alergias crónicas en 2012</t>
+          <t>Población con diagnóstico de alergias crónicas en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19821</t>
+          <t>19074</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40922</t>
+          <t>41587</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33697</t>
+          <t>33734</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>60836</t>
+          <t>61112</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57808</t>
+          <t>59033</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>92559</t>
+          <t>93752</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,7%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>661525</t>
+          <t>660860</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>682626</t>
+          <t>683373</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>636214</t>
+          <t>635938</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>663353</t>
+          <t>663316</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1306938</t>
+          <t>1305745</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1341689</t>
+          <t>1340464</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>95,78%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>42808</t>
+          <t>43407</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74909</t>
+          <t>75223</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65192</t>
+          <t>64397</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>102363</t>
+          <t>99172</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>116238</t>
+          <t>116671</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>162369</t>
+          <t>164441</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,69%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>943038</t>
+          <t>942724</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>975139</t>
+          <t>974540</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,74%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>928546</t>
+          <t>931737</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>965717</t>
+          <t>966512</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,07%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1886487</t>
+          <t>1884415</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1932618</t>
+          <t>1932185</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,31%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29488</t>
+          <t>27921</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55299</t>
+          <t>55669</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,69%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37915</t>
+          <t>37238</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65184</t>
+          <t>65442</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>73897</t>
+          <t>74139</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>113526</t>
+          <t>113895</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,42%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>702324</t>
+          <t>701954</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>728135</t>
+          <t>729702</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>92,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>711990</t>
+          <t>711732</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>739259</t>
+          <t>739936</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,61%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1421271</t>
+          <t>1420902</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1460900</t>
+          <t>1460658</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,17%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>36047</t>
+          <t>34611</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>62051</t>
+          <t>61541</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68620</t>
+          <t>68395</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>105573</t>
+          <t>104016</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>113298</t>
+          <t>111382</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>157917</t>
+          <t>155076</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,76%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>885688</t>
+          <t>886198</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>911692</t>
+          <t>913128</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>946328</t>
+          <t>947885</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>983281</t>
+          <t>983506</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1841723</t>
+          <t>1844564</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1886342</t>
+          <t>1888258</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,43%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>152076</t>
+          <t>150737</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>206038</t>
+          <t>203071</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>224939</t>
+          <t>229317</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>293579</t>
+          <t>293884</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>397343</t>
+          <t>398486</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>480849</t>
+          <t>481127</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,7 +4137,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3219719</t>
+          <t>3222686</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3273681</t>
+          <t>3275020</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3263455</t>
+          <t>3263150</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3332095</t>
+          <t>3327717</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6501941</t>
+          <t>6501663</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6585447</t>
+          <t>6584304</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4255,7 +4255,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,29%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de alergias crónicas en 2016</t>
+          <t>Población con diagnóstico de alergias crónicas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20242</t>
+          <t>20729</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41092</t>
+          <t>42440</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26784</t>
+          <t>27251</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51842</t>
+          <t>52051</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>53208</t>
+          <t>52275</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>84930</t>
+          <t>85303</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>633708</t>
+          <t>632360</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>654558</t>
+          <t>654071</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>620997</t>
+          <t>620788</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>646055</t>
+          <t>645588</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,3%</t>
+          <t>92,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,02%</t>
+          <t>95,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1262709</t>
+          <t>1262336</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1294431</t>
+          <t>1295364</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,12%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33646</t>
+          <t>34418</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>60236</t>
+          <t>61006</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>78119</t>
+          <t>79043</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>117073</t>
+          <t>117765</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,23%</t>
+          <t>11,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>120031</t>
+          <t>120973</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>166821</t>
+          <t>167995</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,08%</t>
+          <t>8,13%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>962195</t>
+          <t>961425</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>988785</t>
+          <t>988013</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>94,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>925840</t>
+          <t>925148</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>964794</t>
+          <t>963870</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,42%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1898523</t>
+          <t>1897349</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1945313</t>
+          <t>1944371</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,92%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,14%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17113</t>
+          <t>17100</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38409</t>
+          <t>38807</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5333,7 +5333,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>49708</t>
+          <t>50225</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>80652</t>
+          <t>81068</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>72073</t>
+          <t>74160</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>110418</t>
+          <t>111127</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,8%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>721143</t>
+          <t>720745</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>742439</t>
+          <t>742452</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,7 +5441,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>704359</t>
+          <t>703943</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>735303</t>
+          <t>734786</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,73%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1434145</t>
+          <t>1433436</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1472490</t>
+          <t>1470403</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,2%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50589</t>
+          <t>51254</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>81707</t>
+          <t>84174</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65862</t>
+          <t>64739</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101030</t>
+          <t>101331</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>124776</t>
+          <t>124264</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>172166</t>
+          <t>172924</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,73%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>855860</t>
+          <t>853393</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>886978</t>
+          <t>886313</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,29%</t>
+          <t>91,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>942749</t>
+          <t>942448</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>977917</t>
+          <t>979040</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,32%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>93,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1809180</t>
+          <t>1808422</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1856570</t>
+          <t>1857082</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,73%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>144483</t>
+          <t>142682</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>194920</t>
+          <t>196124</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>250666</t>
+          <t>242891</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>316062</t>
+          <t>311813</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>410259</t>
+          <t>409329</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>499273</t>
+          <t>495829</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3199430</t>
+          <t>3198226</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3249867</t>
+          <t>3251668</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3228480</t>
+          <t>3232729</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3293876</t>
+          <t>3301651</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>93,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6439619</t>
+          <t>6443063</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6528633</t>
+          <t>6529563</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,8%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,1%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de alergias crónicas en 2023</t>
+          <t>Población con diagnóstico de alergias crónicas en 2023 (tasa de respuesta: 99,73%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43051</t>
+          <t>42934</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>74462</t>
+          <t>76714</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>69328</t>
+          <t>69764</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>98283</t>
+          <t>98437</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>122177</t>
+          <t>121223</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>166196</t>
+          <t>165632</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,66%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>560979</t>
+          <t>558727</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>592390</t>
+          <t>592507</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>574991</t>
+          <t>574837</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>603946</t>
+          <t>603510</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,7%</t>
+          <t>89,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1142519</t>
+          <t>1143083</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1186538</t>
+          <t>1187492</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,74%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47335</t>
+          <t>43067</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>135591</t>
+          <t>133294</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>82503</t>
+          <t>84121</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>114707</t>
+          <t>114272</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>127859</t>
+          <t>122879</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>232448</t>
+          <t>234263</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,91%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1057273</t>
+          <t>1059570</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1145529</t>
+          <t>1149797</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>96,39%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>839835</t>
+          <t>840270</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>872039</t>
+          <t>870421</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>88,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1914958</t>
+          <t>1913143</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2019547</t>
+          <t>2024527</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,28%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>69558</t>
+          <t>67139</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>112141</t>
+          <t>111663</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42376</t>
+          <t>43507</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>121671</t>
+          <t>122272</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,12 +7310,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>113646</t>
+          <t>111125</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>214112</t>
+          <t>216271</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,29%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>588920</t>
+          <t>589398</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>631503</t>
+          <t>633922</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>804740</t>
+          <t>804139</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>884035</t>
+          <t>882904</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,87%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1413359</t>
+          <t>1411200</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1513825</t>
+          <t>1516346</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,84%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,17%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>67635</t>
+          <t>65648</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>110111</t>
+          <t>108482</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,73%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>97224</t>
+          <t>98084</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>146634</t>
+          <t>146291</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>177880</t>
+          <t>175706</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>239136</t>
+          <t>238225</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,83%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>814687</t>
+          <t>816316</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>857163</t>
+          <t>859150</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>942972</t>
+          <t>943315</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>992382</t>
+          <t>991522</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,54%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1775267</t>
+          <t>1776178</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1836523</t>
+          <t>1838697</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,28%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>251169</t>
+          <t>255310</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>374599</t>
+          <t>379206</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>313196</t>
+          <t>320292</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>434456</t>
+          <t>440376</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,79%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>626449</t>
+          <t>623311</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>791239</t>
+          <t>790962</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,14%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3079565</t>
+          <t>3074958</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3202995</t>
+          <t>3198854</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,16%</t>
+          <t>89,02%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3209376</t>
+          <t>3203456</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3330636</t>
+          <t>3323540</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,21%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6306757</t>
+          <t>6307034</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6471547</t>
+          <t>6474685</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,22%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1416-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1416-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25670</t>
+          <t>25552</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47287</t>
+          <t>47983</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>46352</t>
+          <t>45603</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>74495</t>
+          <t>73111</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>75677</t>
+          <t>76568</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>113411</t>
+          <t>114183</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,26%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>646725</t>
+          <t>646029</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>668342</t>
+          <t>668460</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>613856</t>
+          <t>615240</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>641999</t>
+          <t>642748</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1268952</t>
+          <t>1268180</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1306686</t>
+          <t>1305795</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,46%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>56565</t>
+          <t>54949</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>89679</t>
+          <t>88228</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>75669</t>
+          <t>77498</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>114714</t>
+          <t>116306</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>142323</t>
+          <t>141598</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>191567</t>
+          <t>193054</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,0%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>872121</t>
+          <t>873572</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>905235</t>
+          <t>906851</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>853679</t>
+          <t>852087</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>892724</t>
+          <t>890895</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1738626</t>
+          <t>1737139</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1787870</t>
+          <t>1788595</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,63%</t>
+          <t>92,66%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>28483</t>
+          <t>30071</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55151</t>
+          <t>56571</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46846</t>
+          <t>47477</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>74951</t>
+          <t>75984</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>82754</t>
+          <t>82990</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>120521</t>
+          <t>121072</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,89%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>623358</t>
+          <t>621938</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>650026</t>
+          <t>648438</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>608890</t>
+          <t>607857</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>636995</t>
+          <t>636364</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>88,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1241829</t>
+          <t>1241278</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1279596</t>
+          <t>1279360</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,91%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>57445</t>
+          <t>56185</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>88746</t>
+          <t>89228</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,42%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>91544</t>
+          <t>90614</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>131426</t>
+          <t>133265</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,65%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>157557</t>
+          <t>156297</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>208752</t>
+          <t>206246</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,41%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>853476</t>
+          <t>852994</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>884777</t>
+          <t>886037</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,58%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,9%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>907186</t>
+          <t>905347</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>947068</t>
+          <t>947998</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,35%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1772082</t>
+          <t>1774588</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1823277</t>
+          <t>1824537</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>92,11%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>193186</t>
+          <t>188622</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>249909</t>
+          <t>250643</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>290318</t>
+          <t>291854</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>357888</t>
+          <t>358099</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>501629</t>
+          <t>499853</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>590728</t>
+          <t>593898</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,92%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3026634</t>
+          <t>3025900</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3083357</t>
+          <t>3087921</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,37%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3021309</t>
+          <t>3021098</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3088879</t>
+          <t>3087343</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,41%</t>
+          <t>89,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6065013</t>
+          <t>6061843</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6154112</t>
+          <t>6155888</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,12%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>92,49%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19074</t>
+          <t>20477</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>41587</t>
+          <t>42922</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33734</t>
+          <t>32687</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>61112</t>
+          <t>60075</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59033</t>
+          <t>56976</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>93752</t>
+          <t>91503</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>660860</t>
+          <t>659525</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>683373</t>
+          <t>681970</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,28%</t>
+          <t>97,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>635938</t>
+          <t>636975</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>663316</t>
+          <t>664363</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,23%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1305745</t>
+          <t>1307994</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1340464</t>
+          <t>1342521</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,3%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,93%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43407</t>
+          <t>43611</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>75223</t>
+          <t>75034</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>64397</t>
+          <t>63369</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>99172</t>
+          <t>100721</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>116671</t>
+          <t>117332</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>164441</t>
+          <t>163659</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,99%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>942724</t>
+          <t>942913</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>974540</t>
+          <t>974336</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,63%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,72%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>931737</t>
+          <t>930188</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>966512</t>
+          <t>967540</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1884415</t>
+          <t>1885197</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1932185</t>
+          <t>1931524</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,01%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,27%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27921</t>
+          <t>28482</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>55669</t>
+          <t>56819</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37238</t>
+          <t>37967</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65442</t>
+          <t>65319</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>74139</t>
+          <t>72112</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>113895</t>
+          <t>113834</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,7 +3451,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>701954</t>
+          <t>700804</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>729702</t>
+          <t>729141</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>711732</t>
+          <t>711855</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>739936</t>
+          <t>739207</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,58%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1420902</t>
+          <t>1420963</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1460658</t>
+          <t>1462685</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3569,7 +3569,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,3%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34611</t>
+          <t>35574</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>61541</t>
+          <t>61889</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68395</t>
+          <t>68760</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>104016</t>
+          <t>104811</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,89%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>111382</t>
+          <t>111723</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>155076</t>
+          <t>155583</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,78%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>886198</t>
+          <t>885850</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>913128</t>
+          <t>912165</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>947885</t>
+          <t>947090</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>983506</t>
+          <t>983141</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1844564</t>
+          <t>1844057</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1888258</t>
+          <t>1887917</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,41%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>150737</t>
+          <t>149764</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>203071</t>
+          <t>203598</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>229317</t>
+          <t>230262</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>293884</t>
+          <t>293374</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>398486</t>
+          <t>398827</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>481127</t>
+          <t>481472</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,9%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3222686</t>
+          <t>3222159</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3275020</t>
+          <t>3275993</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3263150</t>
+          <t>3263660</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3327717</t>
+          <t>3326772</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6501663</t>
+          <t>6501318</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6584304</t>
+          <t>6583963</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,7 +4250,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20729</t>
+          <t>20527</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42440</t>
+          <t>42066</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27251</t>
+          <t>27367</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>52051</t>
+          <t>51901</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52275</t>
+          <t>52079</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>85303</t>
+          <t>85066</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,31%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>632360</t>
+          <t>632734</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>654071</t>
+          <t>654273</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>96,93%</t>
+          <t>96,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>620788</t>
+          <t>620938</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>645588</t>
+          <t>645472</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>92,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1262336</t>
+          <t>1262573</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1295364</t>
+          <t>1295560</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,14%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34418</t>
+          <t>34001</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61006</t>
+          <t>60921</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>79043</t>
+          <t>80468</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>117765</t>
+          <t>116763</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>120973</t>
+          <t>122781</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>167995</t>
+          <t>168127</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,14%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>961425</t>
+          <t>961510</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>988013</t>
+          <t>988430</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>925148</t>
+          <t>926150</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>963870</t>
+          <t>962445</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,71%</t>
+          <t>88,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,42%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1897349</t>
+          <t>1897217</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1944371</t>
+          <t>1942563</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,06%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17100</t>
+          <t>17630</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38807</t>
+          <t>38109</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>50225</t>
+          <t>47434</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>81068</t>
+          <t>78892</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>74160</t>
+          <t>73167</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>111127</t>
+          <t>111197</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>720745</t>
+          <t>721443</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>742452</t>
+          <t>741922</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>703943</t>
+          <t>706119</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>734786</t>
+          <t>737577</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>89,95%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,96%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1433436</t>
+          <t>1433366</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1470403</t>
+          <t>1471396</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,81%</t>
+          <t>92,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,26%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51254</t>
+          <t>51601</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>84174</t>
+          <t>83006</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64739</t>
+          <t>66010</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101331</t>
+          <t>103026</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>124264</t>
+          <t>125570</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>172924</t>
+          <t>174806</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>853393</t>
+          <t>854561</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>886313</t>
+          <t>885966</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>94,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>942448</t>
+          <t>940753</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>979040</t>
+          <t>977769</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,13%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1808422</t>
+          <t>1806540</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1857082</t>
+          <t>1855776</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,66%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>142682</t>
+          <t>143896</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>196124</t>
+          <t>193843</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>242891</t>
+          <t>250472</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>311813</t>
+          <t>315818</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>409329</t>
+          <t>408350</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>495829</t>
+          <t>493309</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3198226</t>
+          <t>3200507</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3251668</t>
+          <t>3250454</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,22%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3232729</t>
+          <t>3228724</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3301651</t>
+          <t>3294070</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,15%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6443063</t>
+          <t>6445583</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6529563</t>
+          <t>6530542</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,89%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,12%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>57481</t>
+          <t>61478</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>42934</t>
+          <t>47427</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>76714</t>
+          <t>80039</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>83181</t>
+          <t>88110</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>69764</t>
+          <t>73712</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>98437</t>
+          <t>104619</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>140662</t>
+          <t>149588</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>121223</t>
+          <t>129277</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>165632</t>
+          <t>173297</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,26%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>12,19%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>577960</t>
+          <t>629232</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>558727</t>
+          <t>610671</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>592507</t>
+          <t>643283</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>88,41%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>590093</t>
+          <t>642439</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>574837</t>
+          <t>625930</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>603510</t>
+          <t>656837</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>87,65%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,64%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1168053</t>
+          <t>1271670</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1143083</t>
+          <t>1247961</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1187492</t>
+          <t>1291981</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,74%</t>
+          <t>90,9%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>673274</t>
+          <t>730549</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>673274</t>
+          <t>730549</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>673274</t>
+          <t>730549</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1308715</t>
+          <t>1421258</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1308715</t>
+          <t>1421258</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1308715</t>
+          <t>1421258</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>96593</t>
+          <t>99781</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>43067</t>
+          <t>78152</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>133294</t>
+          <t>125419</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>98430</t>
+          <t>112103</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>84121</t>
+          <t>95205</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>114272</t>
+          <t>130988</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>195023</t>
+          <t>211884</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>122879</t>
+          <t>183589</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>234263</t>
+          <t>243358</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,5%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1096271</t>
+          <t>949136</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1059570</t>
+          <t>923498</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1149797</t>
+          <t>970765</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>96,39%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>856112</t>
+          <t>954800</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>840270</t>
+          <t>935915</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>870421</t>
+          <t>971698</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1952383</t>
+          <t>1903936</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1913143</t>
+          <t>1872462</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2024527</t>
+          <t>1932231</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>88,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>91,32%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>954542</t>
+          <t>1066903</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>954542</t>
+          <t>1066903</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>954542</t>
+          <t>1066903</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2147406</t>
+          <t>2115820</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2147406</t>
+          <t>2115820</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2147406</t>
+          <t>2115820</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>86762</t>
+          <t>94297</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>67139</t>
+          <t>75005</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>111663</t>
+          <t>116505</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>12,38%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>87828</t>
+          <t>107383</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>43507</t>
+          <t>90567</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>122272</t>
+          <t>125783</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>13,34%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>174591</t>
+          <t>201680</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>111125</t>
+          <t>176173</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>216271</t>
+          <t>232662</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>12,57%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>14,5%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>614299</t>
+          <t>704981</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>589398</t>
+          <t>682773</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>633922</t>
+          <t>724273</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>87,62%</t>
+          <t>88,2%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>84,07%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>838583</t>
+          <t>697507</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>804139</t>
+          <t>679107</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>882904</t>
+          <t>714323</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>86,66%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>86,8%</t>
+          <t>84,37%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>88,75%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1452880</t>
+          <t>1402488</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1411200</t>
+          <t>1371506</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1516346</t>
+          <t>1427995</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>89,27%</t>
+          <t>87,43%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>85,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>89,02%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>701061</t>
+          <t>799278</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>701061</t>
+          <t>799278</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>701061</t>
+          <t>799278</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>926411</t>
+          <t>804890</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>926411</t>
+          <t>804890</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>926411</t>
+          <t>804890</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1627471</t>
+          <t>1604168</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1627471</t>
+          <t>1604168</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1627471</t>
+          <t>1604168</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>84179</t>
+          <t>87373</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65648</t>
+          <t>69529</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>108482</t>
+          <t>107644</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>7,1%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>123553</t>
+          <t>137586</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>98084</t>
+          <t>118456</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>146291</t>
+          <t>159450</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>207731</t>
+          <t>224959</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>175706</t>
+          <t>198290</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>238225</t>
+          <t>255748</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,16%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>840619</t>
+          <t>900655</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>816316</t>
+          <t>880384</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>859150</t>
+          <t>918499</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>92,9%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>966053</t>
+          <t>977597</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>943315</t>
+          <t>955733</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>991522</t>
+          <t>996727</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>87,66%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1806672</t>
+          <t>1878252</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1776178</t>
+          <t>1847463</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1838697</t>
+          <t>1904921</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,3%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>90,57%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>924798</t>
+          <t>988028</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>924798</t>
+          <t>988028</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>924798</t>
+          <t>988028</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1089606</t>
+          <t>1115183</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1089606</t>
+          <t>1115183</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1089606</t>
+          <t>1115183</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2014403</t>
+          <t>2103211</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2014403</t>
+          <t>2103211</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2014403</t>
+          <t>2103211</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>325015</t>
+          <t>342929</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>255310</t>
+          <t>302109</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>379206</t>
+          <t>386344</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>9,41%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>392992</t>
+          <t>445182</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>320292</t>
+          <t>411567</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>440376</t>
+          <t>484539</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>718007</t>
+          <t>788111</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>623311</t>
+          <t>732522</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>790962</t>
+          <t>840964</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>11,14%</t>
+          <t>11,61%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3129149</t>
+          <t>3184004</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3074958</t>
+          <t>3140589</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3198854</t>
+          <t>3224824</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>90,59%</t>
+          <t>90,28%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3250840</t>
+          <t>3272343</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3203456</t>
+          <t>3232986</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3323540</t>
+          <t>3305958</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>88,02%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6379989</t>
+          <t>6456347</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6307034</t>
+          <t>6403494</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6474685</t>
+          <t>6511936</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>89,88%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>88,86%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>89,89%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3454164</t>
+          <t>3526933</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3454164</t>
+          <t>3526933</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3454164</t>
+          <t>3526933</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3643832</t>
+          <t>3717525</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3643832</t>
+          <t>3717525</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3643832</t>
+          <t>3717525</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7097996</t>
+          <t>7244458</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7097996</t>
+          <t>7244458</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7097996</t>
+          <t>7244458</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
